--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_Portableshop.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_Portableshop.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_Portableshop" sheetId="1" r:id="rId1"/>
@@ -218,7 +218,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -386,13 +386,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -854,7 +847,7 @@
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1628,7 +1621,7 @@
         <v>32</v>
       </c>
       <c r="F7" s="3">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>29</v>
@@ -1651,7 +1644,7 @@
         <v>35</v>
       </c>
       <c r="F8" s="3">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>29</v>
@@ -1674,7 +1667,7 @@
         <v>38</v>
       </c>
       <c r="F9" s="3">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>29</v>
@@ -1720,7 +1713,7 @@
         <v>44</v>
       </c>
       <c r="F11" s="3">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>29</v>
@@ -1743,7 +1736,7 @@
         <v>47</v>
       </c>
       <c r="F12" s="3">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>29</v>
@@ -1766,7 +1759,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="3">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>29</v>
@@ -1812,7 +1805,7 @@
         <v>32</v>
       </c>
       <c r="F15" s="3">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>29</v>
@@ -1835,7 +1828,7 @@
         <v>35</v>
       </c>
       <c r="F16" s="3">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>29</v>
@@ -1864,92 +1857,92 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:7">
       <c r="A18" s="7"/>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
       <c r="E18" s="7"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:7">
       <c r="A19" s="7"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
       <c r="E19" s="7"/>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:7">
       <c r="A20" s="7"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
       <c r="E20" s="7"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:7">
       <c r="A21" s="7"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
       <c r="E21" s="7"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:7">
       <c r="A22" s="7"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="E22" s="7"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:7">
       <c r="A23" s="7"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
       <c r="E23" s="7"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:7">
       <c r="A24" s="7"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
       <c r="E24" s="7"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:7">
       <c r="A25" s="7"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
       <c r="E25" s="7"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:7">
       <c r="A26" s="7"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
       <c r="E26" s="7"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:7">
       <c r="A27" s="7"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
       <c r="E27" s="7"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:7">
       <c r="A28" s="7"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
       <c r="E28" s="7"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:7">
       <c r="A29" s="7"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
       <c r="E29" s="7"/>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:7">
       <c r="A30" s="7"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
       <c r="E30" s="7"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:7">
       <c r="A31" s="7"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
       <c r="E31" s="7"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:7">
       <c r="A32" s="7"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
